--- a/dados/ilc.xlsx
+++ b/dados/ilc.xlsx
@@ -473,7 +473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dados até 07/2026. Arquivo gerado em 30/09/2026.</t>
+          <t>Dados até 08/2026. Arquivo gerado em 30/09/2026.</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1192,7 +1192,7 @@
         <v>44774</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>258.7301</v>
+        <v>258.726</v>
       </c>
     </row>
     <row r="82">
@@ -1568,7 +1568,15 @@
         <v>46204</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>191.892</v>
+        <v>195.2619</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>197.0719</v>
       </c>
     </row>
   </sheetData>
@@ -1582,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2236,7 +2244,7 @@
         <v>44774</v>
       </c>
       <c r="B81" s="6" t="n">
-        <v>-0.003082</v>
+        <v>-0.003097</v>
       </c>
     </row>
     <row r="82">
@@ -2476,7 +2484,7 @@
         <v>45689</v>
       </c>
       <c r="B111" s="6" t="n">
-        <v>-0.000673</v>
+        <v>0.001856</v>
       </c>
     </row>
     <row r="112">
@@ -2484,7 +2492,7 @@
         <v>45717</v>
       </c>
       <c r="B112" s="6" t="n">
-        <v>0.01759</v>
+        <v>0.015021</v>
       </c>
     </row>
     <row r="113">
@@ -2611,7 +2619,17 @@
       <c r="A128" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="B128" s="6" t="n"/>
+      <c r="B128" s="6" t="n">
+        <v>0.012623</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B129" s="6" t="n">
+        <v>0.009268999999999999</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2624,7 +2642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3256,7 +3274,7 @@
         <v>44774</v>
       </c>
       <c r="B81" s="6" t="n">
-        <v>0.007213</v>
+        <v>0.007198</v>
       </c>
     </row>
     <row r="82">
@@ -3496,7 +3514,7 @@
         <v>45689</v>
       </c>
       <c r="B111" s="6" t="n">
-        <v>-0.004597</v>
+        <v>-0.002078</v>
       </c>
     </row>
     <row r="112">
@@ -3631,7 +3649,17 @@
       <c r="A128" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="B128" s="6" t="n"/>
+      <c r="B128" s="6" t="n">
+        <v>0.011085</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B129" s="6" t="n">
+        <v>0.020457</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3644,7 +3672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4276,7 +4304,7 @@
         <v>44774</v>
       </c>
       <c r="B81" s="6" t="n">
-        <v>0.05146</v>
+        <v>0.051444</v>
       </c>
     </row>
     <row r="82">
@@ -4516,7 +4544,7 @@
         <v>45689</v>
       </c>
       <c r="B111" s="6" t="n">
-        <v>0.205952</v>
+        <v>0.209003</v>
       </c>
     </row>
     <row r="112">
@@ -4651,7 +4679,17 @@
       <c r="A128" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="B128" s="6" t="n"/>
+      <c r="B128" s="6" t="n">
+        <v>0.010698</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B129" s="6" t="n">
+        <v>0.010499</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4934,13 +4972,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1959FFA7-D9AF-4668-BF1B-7CC444C93E4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B90E1E-DA37-426F-9D0F-B45574F7404A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E25ED02A-6806-425D-B5BF-9929B5C406DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B54C6987-B52A-48FD-940E-EBB239C9FB7D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{827F3249-E77E-4850-B1B7-73F6BF9C4D42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{184526F9-99A1-418F-B47A-CB745290EC7D}"/>
 </file>
--- a/dados/ilc.xlsx
+++ b/dados/ilc.xlsx
@@ -473,7 +473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dados até 08/2026. Arquivo gerado em 30/09/2026.</t>
+          <t>Dados até 08/2026. Arquivo gerado em 01/10/2026.</t>
         </is>
       </c>
     </row>
@@ -4972,13 +4972,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B90E1E-DA37-426F-9D0F-B45574F7404A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C80AE4D-EF0C-4212-BA2B-8CC72C6C7BA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B54C6987-B52A-48FD-940E-EBB239C9FB7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3749E52-0EA2-4976-A110-5A9478F8AD67}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{184526F9-99A1-418F-B47A-CB745290EC7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9029F83-4688-409B-AFC6-B41ED9CD2F66}"/>
 </file>
--- a/dados/ilc.xlsx
+++ b/dados/ilc.xlsx
@@ -473,7 +473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dados até 08/2026. Arquivo gerado em 01/10/2026.</t>
+          <t>Dados até 09/2026. Arquivo gerado em 29/10/2026.</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1579,6 +1579,14 @@
         <v>197.0719</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>206.765</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1590,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2631,6 +2639,14 @@
         <v>0.009268999999999999</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>0.049186</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2642,7 +2658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3661,6 +3677,14 @@
         <v>0.020457</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>0.070649</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3672,7 +3696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B129"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4689,6 +4713,14 @@
       </c>
       <c r="B129" s="6" t="n">
         <v>0.010499</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>0.06701500000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4972,13 +5004,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C80AE4D-EF0C-4212-BA2B-8CC72C6C7BA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A87EA3-CBBD-439D-8623-A37C55A9F331}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3749E52-0EA2-4976-A110-5A9478F8AD67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96C8EF70-8AB0-44FB-A857-A658ED728B5F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9029F83-4688-409B-AFC6-B41ED9CD2F66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21AC386D-668A-46C2-AE05-9C55B8909262}"/>
 </file>